--- a/Deliverables/BOM/LCD_Board_1.0.3/Client_BOM_LCD_Board_1.0.3.xlsx
+++ b/Deliverables/BOM/LCD_Board_1.0.3/Client_BOM_LCD_Board_1.0.3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\LCD_Board_1.0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACEF5F2-0CEE-4E0C-8AB0-D87903118377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDC15D5-0260-4446-B423-C50318CEB386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,6 +762,10 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -794,10 +798,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1170,13 +1170,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="65"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="67"/>
     </row>
     <row r="2" spans="1:22" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1220,7 +1220,7 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="66"/>
+      <c r="P3" s="68"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1242,7 +1242,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
-      <c r="P4" s="67"/>
+      <c r="P4" s="69"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1264,7 +1264,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="67"/>
+      <c r="P5" s="69"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1282,7 +1282,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="P6" s="67"/>
+      <c r="P6" s="69"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1300,7 +1300,7 @@
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
-      <c r="P7" s="67"/>
+      <c r="P7" s="69"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1318,7 +1318,7 @@
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
-      <c r="P8" s="67"/>
+      <c r="P8" s="69"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1413,8 +1413,8 @@
       </c>
       <c r="O10" s="48"/>
       <c r="P10" s="49"/>
-      <c r="S10" s="74"/>
-      <c r="V10" s="75"/>
+      <c r="S10" s="64"/>
+      <c r="V10" s="65"/>
     </row>
     <row r="11" spans="1:22" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -1461,8 +1461,8 @@
       </c>
       <c r="O11" s="52"/>
       <c r="P11" s="53"/>
-      <c r="S11" s="74"/>
-      <c r="V11" s="75"/>
+      <c r="S11" s="64"/>
+      <c r="V11" s="65"/>
     </row>
     <row r="12" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1476,16 +1476,16 @@
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
       <c r="K12" s="37"/>
-      <c r="L12" s="72" t="s">
+      <c r="L12" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="M12" s="73"/>
+      <c r="M12" s="75"/>
       <c r="N12" s="60">
         <f>SUM(N10:N11)</f>
         <v>3.8983999999999996</v>
       </c>
-      <c r="O12" s="68"/>
-      <c r="P12" s="69"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="71"/>
     </row>
     <row r="13" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -1499,16 +1499,16 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="72" t="s">
+      <c r="L13" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="73"/>
+      <c r="M13" s="75"/>
       <c r="N13" s="61">
         <f>N12/5</f>
         <v>0.77967999999999993</v>
       </c>
-      <c r="O13" s="70"/>
-      <c r="P13" s="71"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
